--- a/artfynd/A 3795-2022 artfynd.xlsx
+++ b/artfynd/A 3795-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122358687</v>
+        <v>122358195</v>
       </c>
       <c r="B2" t="n">
-        <v>98175</v>
+        <v>78645</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,52 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583607</v>
+        <v>583641</v>
       </c>
       <c r="R2" t="n">
-        <v>7041663</v>
+        <v>7041677</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,19 +775,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122358195</v>
+        <v>122357997</v>
       </c>
       <c r="B3" t="n">
         <v>78645</v>
@@ -841,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583641</v>
+        <v>583656</v>
       </c>
       <c r="R3" t="n">
-        <v>7041677</v>
+        <v>7041654</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122358758</v>
+        <v>122358304</v>
       </c>
       <c r="B4" t="n">
-        <v>57374</v>
+        <v>57527</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,27 +915,36 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -958,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583604</v>
+        <v>583622</v>
       </c>
       <c r="R4" t="n">
-        <v>7041656</v>
+        <v>7041674</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,22 +1013,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122358304</v>
+        <v>122358452</v>
       </c>
       <c r="B5" t="n">
-        <v>57527</v>
+        <v>57374</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,36 +1041,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1089,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583622</v>
+        <v>583597</v>
       </c>
       <c r="R5" t="n">
-        <v>7041674</v>
+        <v>7041700</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1134,7 +1115,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,22 +1135,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122357997</v>
+        <v>122358687</v>
       </c>
       <c r="B6" t="n">
-        <v>78645</v>
+        <v>98175</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,38 +1159,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583656</v>
+        <v>583607</v>
       </c>
       <c r="R6" t="n">
-        <v>7041654</v>
+        <v>7041663</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,19 +1261,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122358452</v>
+        <v>122358758</v>
       </c>
       <c r="B7" t="n">
         <v>57374</v>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583597</v>
+        <v>583604</v>
       </c>
       <c r="R7" t="n">
-        <v>7041700</v>
+        <v>7041656</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 3795-2022 artfynd.xlsx
+++ b/artfynd/A 3795-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122358195</v>
+        <v>122358758</v>
       </c>
       <c r="B2" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583641</v>
+        <v>583604</v>
       </c>
       <c r="R2" t="n">
-        <v>7041677</v>
+        <v>7041656</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122357997</v>
+        <v>122358195</v>
       </c>
       <c r="B3" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583656</v>
+        <v>583641</v>
       </c>
       <c r="R3" t="n">
-        <v>7041654</v>
+        <v>7041677</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122358304</v>
+        <v>122358687</v>
       </c>
       <c r="B4" t="n">
-        <v>57527</v>
+        <v>98185</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,40 +921,40 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -953,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583622</v>
+        <v>583607</v>
       </c>
       <c r="R4" t="n">
-        <v>7041674</v>
+        <v>7041663</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122358452</v>
+        <v>122357997</v>
       </c>
       <c r="B5" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,39 +1051,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583597</v>
+        <v>583656</v>
       </c>
       <c r="R5" t="n">
-        <v>7041700</v>
+        <v>7041654</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,12 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122358687</v>
+        <v>122358452</v>
       </c>
       <c r="B6" t="n">
-        <v>98175</v>
+        <v>57374</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,40 +1159,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1201,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583607</v>
+        <v>583597</v>
       </c>
       <c r="R6" t="n">
-        <v>7041663</v>
+        <v>7041700</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1246,7 +1237,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,22 +1257,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122358758</v>
+        <v>122358304</v>
       </c>
       <c r="B7" t="n">
-        <v>57374</v>
+        <v>57527</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1289,27 +1285,36 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1318,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583604</v>
+        <v>583622</v>
       </c>
       <c r="R7" t="n">
-        <v>7041656</v>
+        <v>7041674</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1363,12 +1368,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,12 +1383,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 3795-2022 artfynd.xlsx
+++ b/artfynd/A 3795-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122358758</v>
+        <v>122358687</v>
       </c>
       <c r="B2" t="n">
-        <v>57374</v>
+        <v>98185</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,40 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583604</v>
+        <v>583607</v>
       </c>
       <c r="R2" t="n">
-        <v>7041656</v>
+        <v>7041663</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,22 +789,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122358195</v>
+        <v>122358758</v>
       </c>
       <c r="B3" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,34 +817,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583641</v>
+        <v>583604</v>
       </c>
       <c r="R3" t="n">
-        <v>7041677</v>
+        <v>7041656</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +891,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122358687</v>
+        <v>122358452</v>
       </c>
       <c r="B4" t="n">
-        <v>98185</v>
+        <v>57374</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,40 +935,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -963,10 +968,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583607</v>
+        <v>583597</v>
       </c>
       <c r="R4" t="n">
-        <v>7041663</v>
+        <v>7041700</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1013,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,19 +1033,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122357997</v>
+        <v>122358195</v>
       </c>
       <c r="B5" t="n">
         <v>78646</v>
@@ -1075,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583656</v>
+        <v>583641</v>
       </c>
       <c r="R5" t="n">
-        <v>7041654</v>
+        <v>7041677</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1130,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122358452</v>
+        <v>122358304</v>
       </c>
       <c r="B6" t="n">
-        <v>57374</v>
+        <v>57527</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,27 +1173,36 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1192,10 +1211,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583597</v>
+        <v>583622</v>
       </c>
       <c r="R6" t="n">
-        <v>7041700</v>
+        <v>7041674</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1246,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,12 +1256,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,22 +1271,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122358304</v>
+        <v>122357997</v>
       </c>
       <c r="B7" t="n">
-        <v>57527</v>
+        <v>78646</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,48 +1299,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583622</v>
+        <v>583656</v>
       </c>
       <c r="R7" t="n">
-        <v>7041674</v>
+        <v>7041654</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,12 +1383,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 3795-2022 artfynd.xlsx
+++ b/artfynd/A 3795-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122358687</v>
+        <v>122358452</v>
       </c>
       <c r="B2" t="n">
-        <v>98185</v>
+        <v>57379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,40 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583607</v>
+        <v>583597</v>
       </c>
       <c r="R2" t="n">
-        <v>7041663</v>
+        <v>7041700</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,22 +785,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122358758</v>
+        <v>122358687</v>
       </c>
       <c r="B3" t="n">
-        <v>57374</v>
+        <v>98197</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,31 +809,40 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583604</v>
+        <v>583607</v>
       </c>
       <c r="R3" t="n">
-        <v>7041656</v>
+        <v>7041663</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,12 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,22 +911,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122358452</v>
+        <v>122358195</v>
       </c>
       <c r="B4" t="n">
-        <v>57374</v>
+        <v>78651</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,39 +939,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583597</v>
+        <v>583641</v>
       </c>
       <c r="R4" t="n">
-        <v>7041700</v>
+        <v>7041677</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1013,12 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122358195</v>
+        <v>122357997</v>
       </c>
       <c r="B5" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1085,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583641</v>
+        <v>583656</v>
       </c>
       <c r="R5" t="n">
-        <v>7041677</v>
+        <v>7041654</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122358304</v>
+        <v>122358758</v>
       </c>
       <c r="B6" t="n">
-        <v>57527</v>
+        <v>57379</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,36 +1163,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1211,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583622</v>
+        <v>583604</v>
       </c>
       <c r="R6" t="n">
-        <v>7041674</v>
+        <v>7041656</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1246,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1256,7 +1237,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,22 +1257,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122357997</v>
+        <v>122358304</v>
       </c>
       <c r="B7" t="n">
-        <v>78646</v>
+        <v>57532</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1299,34 +1285,48 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583656</v>
+        <v>583622</v>
       </c>
       <c r="R7" t="n">
-        <v>7041654</v>
+        <v>7041674</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,12 +1383,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 3795-2022 artfynd.xlsx
+++ b/artfynd/A 3795-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122358452</v>
+        <v>122358758</v>
       </c>
       <c r="B2" t="n">
         <v>57379</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583597</v>
+        <v>583604</v>
       </c>
       <c r="R2" t="n">
-        <v>7041700</v>
+        <v>7041656</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122358687</v>
+        <v>122358452</v>
       </c>
       <c r="B3" t="n">
-        <v>98197</v>
+        <v>57379</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,40 +809,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -851,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583607</v>
+        <v>583597</v>
       </c>
       <c r="R3" t="n">
-        <v>7041663</v>
+        <v>7041700</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,22 +907,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122358195</v>
+        <v>122358687</v>
       </c>
       <c r="B4" t="n">
-        <v>78651</v>
+        <v>98202</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,38 +931,52 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583641</v>
+        <v>583607</v>
       </c>
       <c r="R4" t="n">
-        <v>7041677</v>
+        <v>7041663</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +1008,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1018,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,12 +1033,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1147,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122358758</v>
+        <v>122358304</v>
       </c>
       <c r="B6" t="n">
-        <v>57379</v>
+        <v>57532</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,27 +1173,36 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1192,10 +1211,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583604</v>
+        <v>583622</v>
       </c>
       <c r="R6" t="n">
-        <v>7041656</v>
+        <v>7041674</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1246,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,12 +1256,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,22 +1271,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122358304</v>
+        <v>122358195</v>
       </c>
       <c r="B7" t="n">
-        <v>57532</v>
+        <v>78651</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,48 +1299,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583622</v>
+        <v>583641</v>
       </c>
       <c r="R7" t="n">
-        <v>7041674</v>
+        <v>7041677</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,12 +1383,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 3795-2022 artfynd.xlsx
+++ b/artfynd/A 3795-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122358758</v>
+        <v>122357997</v>
       </c>
       <c r="B2" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583604</v>
+        <v>583656</v>
       </c>
       <c r="R2" t="n">
-        <v>7041656</v>
+        <v>7041654</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122358452</v>
+        <v>122358758</v>
       </c>
       <c r="B3" t="n">
         <v>57379</v>
@@ -815,11 +800,6 @@
       <c r="E3" t="n">
         <v>100109</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -842,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583597</v>
+        <v>583604</v>
       </c>
       <c r="R3" t="n">
-        <v>7041700</v>
+        <v>7041656</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -919,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122358687</v>
+        <v>122358452</v>
       </c>
       <c r="B4" t="n">
-        <v>98202</v>
+        <v>57379</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,40 +911,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -973,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583607</v>
+        <v>583597</v>
       </c>
       <c r="R4" t="n">
-        <v>7041663</v>
+        <v>7041700</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1018,7 +984,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,22 +1004,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122357997</v>
+        <v>122358304</v>
       </c>
       <c r="B5" t="n">
-        <v>78651</v>
+        <v>57532</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1061,34 +1032,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>103021</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583656</v>
+        <v>583622</v>
       </c>
       <c r="R5" t="n">
-        <v>7041654</v>
+        <v>7041674</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,22 +1125,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122358304</v>
+        <v>122358687</v>
       </c>
       <c r="B6" t="n">
-        <v>57532</v>
+        <v>98211</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,40 +1149,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1211,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583622</v>
+        <v>583607</v>
       </c>
       <c r="R6" t="n">
-        <v>7041674</v>
+        <v>7041663</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1246,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1256,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1286,7 +1261,7 @@
         <v>122358195</v>
       </c>
       <c r="B7" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,11 +1275,6 @@
       </c>
       <c r="E7" t="n">
         <v>6425</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>

--- a/artfynd/A 3795-2022 artfynd.xlsx
+++ b/artfynd/A 3795-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122357997</v>
+        <v>122358452</v>
       </c>
       <c r="B2" t="n">
-        <v>78652</v>
+        <v>57383</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,29 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583656</v>
+        <v>583597</v>
       </c>
       <c r="R2" t="n">
-        <v>7041654</v>
+        <v>7041700</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122358758</v>
+        <v>122358687</v>
       </c>
       <c r="B3" t="n">
-        <v>57379</v>
+        <v>98224</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,26 +809,40 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -822,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583604</v>
+        <v>583607</v>
       </c>
       <c r="R3" t="n">
-        <v>7041656</v>
+        <v>7041663</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +911,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122358452</v>
+        <v>122357997</v>
       </c>
       <c r="B4" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +939,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583597</v>
+        <v>583656</v>
       </c>
       <c r="R4" t="n">
-        <v>7041700</v>
+        <v>7041654</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,12 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,7 +1038,7 @@
         <v>122358304</v>
       </c>
       <c r="B5" t="n">
-        <v>57532</v>
+        <v>57536</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,6 +1052,11 @@
       </c>
       <c r="E5" t="n">
         <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1137,10 +1161,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122358687</v>
+        <v>122358195</v>
       </c>
       <c r="B6" t="n">
-        <v>98211</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,47 +1173,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583607</v>
+        <v>583641</v>
       </c>
       <c r="R6" t="n">
-        <v>7041663</v>
+        <v>7041677</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,7 +1236,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1246,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,22 +1261,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122358195</v>
+        <v>122358758</v>
       </c>
       <c r="B7" t="n">
-        <v>78652</v>
+        <v>57383</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,29 +1289,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583641</v>
+        <v>583604</v>
       </c>
       <c r="R7" t="n">
-        <v>7041677</v>
+        <v>7041656</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,7 +1353,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1363,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 3795-2022 artfynd.xlsx
+++ b/artfynd/A 3795-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122358452</v>
+        <v>122358195</v>
       </c>
       <c r="B2" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583597</v>
+        <v>583641</v>
       </c>
       <c r="R2" t="n">
-        <v>7041700</v>
+        <v>7041677</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122358687</v>
+        <v>122358758</v>
       </c>
       <c r="B3" t="n">
-        <v>98224</v>
+        <v>57383</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,40 +799,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -851,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583607</v>
+        <v>583604</v>
       </c>
       <c r="R3" t="n">
-        <v>7041663</v>
+        <v>7041656</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122357997</v>
+        <v>122358687</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>98237</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,38 +921,52 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583656</v>
+        <v>583607</v>
       </c>
       <c r="R4" t="n">
-        <v>7041654</v>
+        <v>7041663</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,22 +1023,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122358304</v>
+        <v>122357997</v>
       </c>
       <c r="B5" t="n">
-        <v>57536</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,48 +1051,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583622</v>
+        <v>583656</v>
       </c>
       <c r="R5" t="n">
-        <v>7041674</v>
+        <v>7041654</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1134,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,22 +1135,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122358195</v>
+        <v>122358452</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1177,34 +1163,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583641</v>
+        <v>583597</v>
       </c>
       <c r="R6" t="n">
-        <v>7041677</v>
+        <v>7041700</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1246,7 +1237,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122358758</v>
+        <v>122358304</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
+        <v>57536</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1289,27 +1285,36 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1318,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583604</v>
+        <v>583622</v>
       </c>
       <c r="R7" t="n">
-        <v>7041656</v>
+        <v>7041674</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1363,12 +1368,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,12 +1383,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 3795-2022 artfynd.xlsx
+++ b/artfynd/A 3795-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122358195</v>
+        <v>122357997</v>
       </c>
       <c r="B2" t="n">
         <v>78656</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583641</v>
+        <v>583656</v>
       </c>
       <c r="R2" t="n">
-        <v>7041677</v>
+        <v>7041654</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122358758</v>
+        <v>122358195</v>
       </c>
       <c r="B3" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583604</v>
+        <v>583641</v>
       </c>
       <c r="R3" t="n">
-        <v>7041656</v>
+        <v>7041677</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122358687</v>
+        <v>122358452</v>
       </c>
       <c r="B4" t="n">
-        <v>98237</v>
+        <v>57383</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,40 +911,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -963,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583607</v>
+        <v>583597</v>
       </c>
       <c r="R4" t="n">
-        <v>7041663</v>
+        <v>7041700</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,22 +1009,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122357997</v>
+        <v>122358758</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,34 +1037,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583656</v>
+        <v>583604</v>
       </c>
       <c r="R5" t="n">
-        <v>7041654</v>
+        <v>7041656</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122358452</v>
+        <v>122358304</v>
       </c>
       <c r="B6" t="n">
-        <v>57383</v>
+        <v>57536</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,27 +1159,36 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1192,10 +1197,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583597</v>
+        <v>583622</v>
       </c>
       <c r="R6" t="n">
-        <v>7041700</v>
+        <v>7041674</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,12 +1242,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,22 +1257,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122358304</v>
+        <v>122358687</v>
       </c>
       <c r="B7" t="n">
-        <v>57536</v>
+        <v>98237</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,40 +1281,40 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583622</v>
+        <v>583607</v>
       </c>
       <c r="R7" t="n">
-        <v>7041674</v>
+        <v>7041663</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 3795-2022 artfynd.xlsx
+++ b/artfynd/A 3795-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122357997</v>
+        <v>122358687</v>
       </c>
       <c r="B2" t="n">
-        <v>78656</v>
+        <v>98240</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,52 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583656</v>
+        <v>583607</v>
       </c>
       <c r="R2" t="n">
-        <v>7041654</v>
+        <v>7041663</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,19 +789,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122358195</v>
+        <v>122357997</v>
       </c>
       <c r="B3" t="n">
         <v>78656</v>
@@ -827,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583641</v>
+        <v>583656</v>
       </c>
       <c r="R3" t="n">
-        <v>7041677</v>
+        <v>7041654</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1021,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122358758</v>
+        <v>122358195</v>
       </c>
       <c r="B5" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,39 +1051,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583604</v>
+        <v>583641</v>
       </c>
       <c r="R5" t="n">
-        <v>7041656</v>
+        <v>7041677</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1269,10 +1273,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122358687</v>
+        <v>122358758</v>
       </c>
       <c r="B7" t="n">
-        <v>98237</v>
+        <v>57383</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,40 +1285,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1323,10 +1318,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583607</v>
+        <v>583604</v>
       </c>
       <c r="R7" t="n">
-        <v>7041663</v>
+        <v>7041656</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1358,7 +1353,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,7 +1363,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,12 +1383,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 3795-2022 artfynd.xlsx
+++ b/artfynd/A 3795-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122358687</v>
+        <v>122358758</v>
       </c>
       <c r="B2" t="n">
-        <v>98240</v>
+        <v>57383</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,40 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583607</v>
+        <v>583604</v>
       </c>
       <c r="R2" t="n">
-        <v>7041663</v>
+        <v>7041656</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,22 +785,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122357997</v>
+        <v>122358452</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,34 +813,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583656</v>
+        <v>583597</v>
       </c>
       <c r="R3" t="n">
-        <v>7041654</v>
+        <v>7041700</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122358452</v>
+        <v>122358195</v>
       </c>
       <c r="B4" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,39 +935,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583597</v>
+        <v>583641</v>
       </c>
       <c r="R4" t="n">
-        <v>7041700</v>
+        <v>7041677</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122358195</v>
+        <v>122358687</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>98240</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,38 +1043,52 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583641</v>
+        <v>583607</v>
       </c>
       <c r="R5" t="n">
-        <v>7041677</v>
+        <v>7041663</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1130,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,12 +1145,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1273,10 +1283,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122358758</v>
+        <v>122357997</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1289,39 +1299,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583604</v>
+        <v>583656</v>
       </c>
       <c r="R7" t="n">
-        <v>7041656</v>
+        <v>7041654</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1363,12 +1368,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 3795-2022 artfynd.xlsx
+++ b/artfynd/A 3795-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122358758</v>
       </c>
       <c r="B2" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122358452</v>
+        <v>122358687</v>
       </c>
       <c r="B3" t="n">
-        <v>57383</v>
+        <v>98241</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,31 +809,40 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583597</v>
+        <v>583607</v>
       </c>
       <c r="R3" t="n">
-        <v>7041700</v>
+        <v>7041663</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,22 +911,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122358195</v>
+        <v>122358452</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,34 +939,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583641</v>
+        <v>583597</v>
       </c>
       <c r="R4" t="n">
-        <v>7041677</v>
+        <v>7041700</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1013,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122358687</v>
+        <v>122357997</v>
       </c>
       <c r="B5" t="n">
-        <v>98240</v>
+        <v>78657</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,52 +1057,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583607</v>
+        <v>583656</v>
       </c>
       <c r="R5" t="n">
-        <v>7041663</v>
+        <v>7041654</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,12 +1145,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1160,7 +1160,7 @@
         <v>122358304</v>
       </c>
       <c r="B6" t="n">
-        <v>57536</v>
+        <v>57537</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1283,10 +1283,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122357997</v>
+        <v>122358195</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583656</v>
+        <v>583641</v>
       </c>
       <c r="R7" t="n">
-        <v>7041654</v>
+        <v>7041677</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 3795-2022 artfynd.xlsx
+++ b/artfynd/A 3795-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122358758</v>
+        <v>122358195</v>
       </c>
       <c r="B2" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583604</v>
+        <v>583641</v>
       </c>
       <c r="R2" t="n">
-        <v>7041656</v>
+        <v>7041677</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122358687</v>
+        <v>122358452</v>
       </c>
       <c r="B3" t="n">
-        <v>98241</v>
+        <v>57384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,40 +799,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -851,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583607</v>
+        <v>583597</v>
       </c>
       <c r="R3" t="n">
-        <v>7041663</v>
+        <v>7041700</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,19 +897,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122358452</v>
+        <v>122358758</v>
       </c>
       <c r="B4" t="n">
         <v>57384</v>
@@ -968,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583597</v>
+        <v>583604</v>
       </c>
       <c r="R4" t="n">
-        <v>7041700</v>
+        <v>7041656</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1013,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1045,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122357997</v>
+        <v>122358687</v>
       </c>
       <c r="B5" t="n">
-        <v>78657</v>
+        <v>98244</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,38 +1043,52 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583656</v>
+        <v>583607</v>
       </c>
       <c r="R5" t="n">
-        <v>7041654</v>
+        <v>7041663</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,22 +1145,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122358304</v>
+        <v>122357997</v>
       </c>
       <c r="B6" t="n">
-        <v>57537</v>
+        <v>78660</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,48 +1173,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583622</v>
+        <v>583656</v>
       </c>
       <c r="R6" t="n">
-        <v>7041674</v>
+        <v>7041654</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1246,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1256,7 +1242,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,22 +1257,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122358195</v>
+        <v>122358304</v>
       </c>
       <c r="B7" t="n">
-        <v>78657</v>
+        <v>57537</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1299,34 +1285,48 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583641</v>
+        <v>583622</v>
       </c>
       <c r="R7" t="n">
-        <v>7041677</v>
+        <v>7041674</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,12 +1383,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 3795-2022 artfynd.xlsx
+++ b/artfynd/A 3795-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122358195</v>
+        <v>122358304</v>
       </c>
       <c r="B2" t="n">
-        <v>78660</v>
+        <v>57537</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583641</v>
+        <v>583622</v>
       </c>
       <c r="R2" t="n">
-        <v>7041677</v>
+        <v>7041674</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +789,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122358452</v>
+        <v>122357997</v>
       </c>
       <c r="B3" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +817,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583597</v>
+        <v>583656</v>
       </c>
       <c r="R3" t="n">
-        <v>7041700</v>
+        <v>7041654</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122358758</v>
+        <v>122358452</v>
       </c>
       <c r="B4" t="n">
         <v>57384</v>
@@ -954,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583604</v>
+        <v>583597</v>
       </c>
       <c r="R4" t="n">
-        <v>7041656</v>
+        <v>7041700</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1031,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122358687</v>
+        <v>122358758</v>
       </c>
       <c r="B5" t="n">
-        <v>98244</v>
+        <v>57384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,40 +1047,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1085,10 +1080,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583607</v>
+        <v>583604</v>
       </c>
       <c r="R5" t="n">
-        <v>7041663</v>
+        <v>7041656</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,7 +1125,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,22 +1145,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122357997</v>
+        <v>122358687</v>
       </c>
       <c r="B6" t="n">
-        <v>78660</v>
+        <v>98244</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,38 +1169,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583656</v>
+        <v>583607</v>
       </c>
       <c r="R6" t="n">
-        <v>7041654</v>
+        <v>7041663</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,7 +1246,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,7 +1256,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,22 +1271,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122358304</v>
+        <v>122358195</v>
       </c>
       <c r="B7" t="n">
-        <v>57537</v>
+        <v>78660</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,48 +1299,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583622</v>
+        <v>583641</v>
       </c>
       <c r="R7" t="n">
-        <v>7041674</v>
+        <v>7041677</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,12 +1383,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 3795-2022 artfynd.xlsx
+++ b/artfynd/A 3795-2022 artfynd.xlsx
@@ -675,64 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122358304</v>
+        <v>122357997</v>
       </c>
       <c r="B2" t="n">
-        <v>57537</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583622</v>
+        <v>583656</v>
       </c>
       <c r="R2" t="n">
-        <v>7041674</v>
+        <v>7041654</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,31 +770,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122357997</v>
+        <v>122358195</v>
       </c>
       <c r="B3" t="n">
-        <v>78660</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -841,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583656</v>
+        <v>583641</v>
       </c>
       <c r="R3" t="n">
-        <v>7041654</v>
+        <v>7041677</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,12 +892,7 @@
         <v>122358452</v>
       </c>
       <c r="B4" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,12 +1009,7 @@
         <v>122358758</v>
       </c>
       <c r="B5" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,52 +1123,47 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122358687</v>
+        <v>122358304</v>
       </c>
       <c r="B6" t="n">
-        <v>98244</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1211,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583607</v>
+        <v>583622</v>
       </c>
       <c r="R6" t="n">
-        <v>7041663</v>
+        <v>7041674</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1246,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1256,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1283,50 +1244,59 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122358195</v>
+        <v>122358687</v>
       </c>
       <c r="B7" t="n">
-        <v>78660</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tosklokklippen, Tosklokklippen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583641</v>
+        <v>583607</v>
       </c>
       <c r="R7" t="n">
-        <v>7041677</v>
+        <v>7041663</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1358,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,12 +1353,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 3795-2022 artfynd.xlsx
+++ b/artfynd/A 3795-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122357997</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122358195</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122358452</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122358758</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1241,6 +1266,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122358304</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1362,8 +1392,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122358687</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>